--- a/tests/data/test_scenarios/test_1/separate/test_bid_file4.xlsx
+++ b/tests/data/test_scenarios/test_1/separate/test_bid_file4.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHWATES\OneDrive - kochind.com\Documents\Ad hoc\RFP Analysis Automation Files\OneDrive_2024-09-16\RFP Submissions\RFP data test\Dummy data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chrisw78\RFP Automation REPO\RFP_Analysis_Automation2\tests\data\test_scenarios\test_1\separate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1680700C-F9A4-4822-890E-8289DC06B506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E6CDF8-E66D-4FF1-BE69-56263BE1ACEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3225" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{C7C76E7D-3BFC-40C3-A3F6-6B86DDE7E996}"/>
+    <workbookView xWindow="-28920" yWindow="1890" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C7C76E7D-3BFC-40C3-A3F6-6B86DDE7E996}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="rebates" sheetId="2" r:id="rId2"/>
+    <sheet name="capacity" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>Bid ID</t>
   </si>
@@ -56,9 +58,6 @@
     <t>Facility</t>
   </si>
   <si>
-    <t>Supplier 4</t>
-  </si>
-  <si>
     <t>Facility 1</t>
   </si>
   <si>
@@ -72,6 +71,39 @@
   </si>
   <si>
     <t>Facility 5</t>
+  </si>
+  <si>
+    <t>Jared</t>
+  </si>
+  <si>
+    <t>Supplier Name</t>
+  </si>
+  <si>
+    <t>Grouping</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Modified</t>
+  </si>
+  <si>
+    <t>Min Volume</t>
+  </si>
+  <si>
+    <t>Max Volume</t>
+  </si>
+  <si>
+    <t>Min Spend</t>
+  </si>
+  <si>
+    <t>Max Spend</t>
+  </si>
+  <si>
+    <t>% Rebate</t>
+  </si>
+  <si>
+    <t>$ Rebate</t>
   </si>
 </sst>
 </file>
@@ -81,10 +113,25 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -110,9 +157,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -482,7 +533,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>3437457</v>
@@ -494,7 +545,7 @@
         <v>0.23792059927489834</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -502,7 +553,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>3001110</v>
@@ -514,7 +565,7 @@
         <v>0.96352612656699033</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -522,7 +573,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>24000</v>
@@ -534,7 +585,7 @@
         <v>0.812129340958895</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -542,7 +593,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>357800</v>
@@ -554,7 +605,7 @@
         <v>1.4407637142680829</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -562,7 +613,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>45000</v>
@@ -574,7 +625,78 @@
         <v>0.45905772765551361</v>
       </c>
       <c r="F6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="GUID" r:id="rId1"/>
+  </customProperties>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D54790C-7306-47AD-AA15-5E8D61F5E488}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="GUID" r:id="rId1"/>
+  </customProperties>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5683169-B3EE-403A-A5E7-8262B937F9F7}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>
